--- a/examples/OpenAI/test_prompts_pdf.xlsx
+++ b/examples/OpenAI/test_prompts_pdf.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t xml:space="preserve">name</t>
   </si>
@@ -65,6 +65,9 @@
   </si>
   <si>
     <t xml:space="preserve">skip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Write anything you want!</t>
   </si>
   <si>
     <t xml:space="preserve">#py def my_skip_test(answer, param):
@@ -72,16 +75,15 @@
   Return True</t>
   </si>
   <si>
-    <t xml:space="preserve">Write anything you want!</t>
+    <t xml:space="preserve">This prompt will not be reached if the skipPrompt triggers</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="&quot;TRUE&quot;;&quot;TRUE&quot;;&quot;FALSE&quot;"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -149,7 +151,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -159,14 +161,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -362,9 +356,11 @@
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="35.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="49.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="7.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="8.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="56.92"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -430,20 +426,21 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="3" t="b">
+      <c r="C5" s="1" t="n">
+        <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="D5" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E5" s="4" t="s">
+      <c r="D5" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="E5" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="F5" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
